--- a/プログラムバージョン管理/プログラムバージョン管理.xlsx
+++ b/プログラムバージョン管理/プログラムバージョン管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\117029\Documents\Git\myTest\プログラムバージョン管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D52FB73-D63B-433D-B3EE-A9B4DCADA53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948B4797-0E34-4782-AB4C-AA4172448FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D18C1AD2-2E52-4420-B1DC-0C9A56BE94AE}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D18C1AD2-2E52-4420-B1DC-0C9A56BE94AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>コントローラバージョンの付け方</t>
-    <rPh sb="12" eb="13">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>・V1.00から開始</t>
     <rPh sb="8" eb="10">
@@ -303,63 +293,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Gitによる管理</t>
-    <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PLUS+1のプログラム管理</t>
-    <rPh sb="12" eb="14">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>└ #####-##bbb(bbbbb)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・src … PLUS+1のプログラムを保存する</t>
-    <rPh sb="20" eb="22">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・tmp … Githubにpushした時に、自動でlhx,scsにバージョンが付いて保存される</t>
-    <rPh sb="20" eb="21">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・release … mainブランチにマージした時に、自動でlhx、scsにバージョンが付いて保存される（通常は</t>
-    <rPh sb="25" eb="26">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>ツウジョウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -442,9 +376,287 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・HistoryLog.txt(来歴)、Application_ID.txtも</t>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> … PLUS+1のプログラムを保存する</t>
+    </r>
+    <rPh sb="20" eb="22">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tmp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> … Githubにpushした時に、自動でlhx,scsにバージョンが付いて保存される</t>
+    </r>
+    <rPh sb="20" eb="21">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>release</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> … mainブランチにマージした時に、自動でlhx、scsにバージョンが付いて保存される</t>
+    </r>
+    <rPh sb="25" eb="26">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【PLUS+1のプログラム管理】</t>
+    <rPh sb="13" eb="15">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【Gitによる管理】</t>
+    <rPh sb="7" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【コントローラバージョンの付け方】</t>
+    <rPh sb="13" eb="14">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・HistoryLog.txt(来歴)、Application_ID.txtもPLUS+1のプロジェクトに追加する</t>
     <rPh sb="16" eb="18">
       <t>ライレキ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（ファイルの変更箇所を確認しやすいようにするため）</t>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（Gitで管理するファイルを明確にするため）</t>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・新規品番を設定する場合、ベースのバージョンのプロジェクトをコピーして、コミットしてから変更を行うこと</t>
+    <rPh sb="1" eb="3">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒンバン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（どのバージョンから、どこを変えたのかわかるようにすること）</t>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Description: 開発コード(例:A13AW)</t>
+    <rPh sb="13" eb="15">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>System ID: 空白</t>
+    <rPh sb="11" eb="13">
+      <t>クウハク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[Application Data]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[Tool Key]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ServiceToolDataの各パラメータ</t>
+    <rPh sb="17" eb="18">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Type: 商品名_品番下5桁(例:TB370W_00189)…Typeが一致していないプログラムを上書きする場合、上書きするプログラムのTypeを入力する必要がある</t>
+    <rPh sb="6" eb="9">
+      <t>ショウヒンメイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒンバン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>シモ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOGKEY: 開発コード(例:A13AW)…サービスツールの設定に使用する</t>
+    <rPh sb="8" eb="10">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -453,7 +665,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,6 +687,15 @@
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -499,12 +720,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2128,12 +2355,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>120806</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>157370</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>46464</xdr:rowOff>
+      <xdr:rowOff>29899</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1300976" cy="412727"/>
+    <xdr:ext cx="2042978" cy="412727"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="99" name="吹き出し: 角を丸めた四角形 98">
@@ -2147,13 +2374,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2727404" y="7155366"/>
-          <a:ext cx="1300976" cy="412727"/>
+          <a:off x="637761" y="6755377"/>
+          <a:ext cx="2042978" cy="412727"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 41220"/>
-            <a:gd name="adj2" fmla="val 189510"/>
+            <a:gd name="adj1" fmla="val 31895"/>
+            <a:gd name="adj2" fmla="val 191517"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -2174,7 +2401,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="t">
+        <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="t">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -2186,11 +2413,26 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700"/>
-            <a:t>main</a:t>
+            <a:t>pull request</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="700"/>
-            <a:t>にマージする</a:t>
+            <a:t>する</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="700"/>
+            <a:t>（リポジトリの管理者が</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700"/>
+            <a:t>marge</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="700"/>
+            <a:t>する）</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2641,6 +2883,239 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>212587</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F12042F-9DCF-8C4C-DA2C-D9FDF2CB2326}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="521804" y="13103087"/>
+          <a:ext cx="2882348" cy="1761435"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>63338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>124240</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>183700</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="26" name="グループ化 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C91E2E4-F4A6-0709-12A4-9B651151C252}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1441174" y="13033903"/>
+          <a:ext cx="6849718" cy="3483101"/>
+          <a:chOff x="2758108" y="12909664"/>
+          <a:chExt cx="6849718" cy="3483101"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="17" name="図 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4E04C95-5E27-63C3-B912-A9648B73B443}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5044109" y="12970566"/>
+            <a:ext cx="4563717" cy="3218615"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="フローチャート: 代替処理 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0554FD5E-81B0-58D9-3252-A1631791A937}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4994413" y="12909664"/>
+            <a:ext cx="2496476" cy="3329122"/>
+          </a:xfrm>
+          <a:prstGeom prst="flowChartAlternateProcess">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="31750">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="24" name="吹き出し: 角を丸めた四角形 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F32A656-CE4D-CA6A-A530-D22AC30F8DF8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2758108" y="15506991"/>
+            <a:ext cx="1962004" cy="885774"/>
+          </a:xfrm>
+          <a:prstGeom prst="wedgeRoundRectCallout">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 62159"/>
+              <a:gd name="adj2" fmla="val -36616"/>
+              <a:gd name="adj3" fmla="val 16667"/>
+            </a:avLst>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="overflow" horzOverflow="overflow" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>Project</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>View</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>で左側に表示されたファイルのみを</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>Git</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+              <a:t>の管理対象とする</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2961,159 +3436,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44D8449-A153-4719-8B67-7453ACE50D2D}">
-  <dimension ref="B1:F51"/>
+  <dimension ref="B1:F80"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" t="s">
-        <v>17</v>
+      <c r="B39" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D41" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="E42" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="E44" s="1"/>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="E45" s="1"/>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B49" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C50" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C73" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D76" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D77" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D78" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D80" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
